--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N176_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N176_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.25896865968443</v>
+        <v>2.31708240719872</v>
       </c>
       <c r="D2" t="n">
-        <v>13.41298888668831</v>
+        <v>2.17961069408685</v>
       </c>
       <c r="E2" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F2" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.392984582854125</v>
+        <v>1.038859994713795</v>
       </c>
       <c r="D3" t="n">
-        <v>9.095025639618429</v>
+        <v>1.477941666437995</v>
       </c>
       <c r="E3" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F3" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.310044652240241</v>
+        <v>1.187882255989039</v>
       </c>
       <c r="D4" t="n">
-        <v>14.13337306368413</v>
+        <v>2.296673122848671</v>
       </c>
       <c r="E4" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F4" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.39371327986881</v>
+        <v>3.476478407978681</v>
       </c>
       <c r="D5" t="n">
-        <v>20.54329542800129</v>
+        <v>3.338285507050209</v>
       </c>
       <c r="E5" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F5" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.000844548262481</v>
+        <v>1.137637239092653</v>
       </c>
       <c r="D6" t="n">
-        <v>7.973763406582407</v>
+        <v>1.295736553569641</v>
       </c>
       <c r="E6" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F6" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.5069465872347</v>
+        <v>8.857378820425639</v>
       </c>
       <c r="D7" t="n">
-        <v>53.08297257561306</v>
+        <v>8.625983043537122</v>
       </c>
       <c r="E7" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F7" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.24477022903979</v>
+        <v>4.102275162218966</v>
       </c>
       <c r="D8" t="n">
-        <v>25.55003865571718</v>
+        <v>4.151881281554042</v>
       </c>
       <c r="E8" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F8" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.47535909324613</v>
+        <v>2.514745852652497</v>
       </c>
       <c r="D9" t="n">
-        <v>14.79000627235786</v>
+        <v>2.403376019258152</v>
       </c>
       <c r="E9" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F9" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.38372094906639</v>
+        <v>6.074854654223288</v>
       </c>
       <c r="D10" t="n">
-        <v>38.64599780230147</v>
+        <v>6.279974642873988</v>
       </c>
       <c r="E10" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F10" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.29993404049348</v>
+        <v>7.361239281580191</v>
       </c>
       <c r="D11" t="n">
-        <v>43.93582930531593</v>
+        <v>7.139572262113838</v>
       </c>
       <c r="E11" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F11" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>43.09201660718583</v>
+        <v>7.002452698667697</v>
       </c>
       <c r="D12" t="n">
-        <v>42.05773053941684</v>
+        <v>6.834381212655236</v>
       </c>
       <c r="E12" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F12" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.39644226210489</v>
+        <v>6.889421867592045</v>
       </c>
       <c r="D13" t="n">
-        <v>41.99432814965952</v>
+        <v>6.824078324319672</v>
       </c>
       <c r="E13" t="n">
-        <v>16.42106321011283</v>
+        <v>2.668422771643335</v>
       </c>
       <c r="F13" t="n">
-        <v>15.22014341712244</v>
+        <v>2.473273305282396</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
